--- a/chemical_adsorbent_report.xlsx
+++ b/chemical_adsorbent_report.xlsx
@@ -12,11 +12,13 @@
     <sheet name="Dataset" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Training Data" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Testing &amp; Predictions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Model Metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Coefficients" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Statistical Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Correlation Matrix" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Graph Analysis" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="All Predictions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Metal Combinations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Model Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Coefficients" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Statistical Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correlation Matrix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Graph Analysis" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,6 +507,679 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ce (mg/L)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>qe (mg/g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11.75694444444444</v>
+      </c>
+      <c r="I3" t="n">
+        <v>76.48611111111111</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.07061111111111</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5669467095138409</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.20458932936041</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.242118006816238</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34.01680257083045</v>
+      </c>
+      <c r="F4" t="n">
+        <v>42.04589329360411</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.740102322561517</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19.48020464512303</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.42200022144531</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.84375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>175</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.5835</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I8" t="n">
+        <v>92</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>120</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ce (mg/L)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>qe (mg/g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9438798074485388</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9128709291752771</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9438798074485392</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.8191084467312126</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8191084467312126</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.817176499196376</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9438798074485388</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7385489458759963</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9438798074485387</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.6939553253752606</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6939553253752606</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.7261631278865359</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9128709291752771</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7385489458759963</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9128709291752768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9847319278346622</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.8495841102831636</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8495841102831634</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.8035728671246343</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9438798074485387</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9128709291752768</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9438798074485392</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.8191084467312125</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8191084467312125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.8171764991963759</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9438798074485392</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9847319278346622</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9438798074485392</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.8443886192831871</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8443886192831872</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.8112383490526567</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ce (mg/L)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.8191084467312126</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.6939553253752606</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8495841102831636</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.8191084467312125</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.8443886192831871</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4445206645340559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8191084467312126</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6939553253752606</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8495841102831634</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8191084467312125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8443886192831872</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.444520664534056</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>qe (mg/g)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.817176499196376</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.7261631278865359</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.8035728671246343</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.8171764991963759</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.8112383490526567</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4445206645340559</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.444520664534056</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -532,7 +1207,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R2: 0.982 | RMSE: 2.266</t>
+          <t>R2: 0.988 | RMSE: 1.894</t>
         </is>
       </c>
     </row>
@@ -544,7 +1219,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R2: 0.967 | RMSE: 4.496</t>
+          <t>R2: 0.992 | RMSE: 2.267</t>
         </is>
       </c>
     </row>
@@ -556,7 +1231,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mean: -2.805 | Std: 3.513</t>
+          <t>Mean: -1.050 | Std: 2.009</t>
         </is>
       </c>
     </row>
@@ -568,7 +1243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Median abs error: 2.838</t>
+          <t>Median abs error: 1.400</t>
         </is>
       </c>
     </row>
@@ -580,7 +1255,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mean abs error: 3.399</t>
+          <t>Mean abs error: 1.775</t>
         </is>
       </c>
     </row>
@@ -607,10 +1282,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -648,7 +1323,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>February 23, 2026</t>
+          <t>March 7, 2026</t>
         </is>
       </c>
     </row>
@@ -696,7 +1371,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9674</v>
+        <v>0.9917</v>
       </c>
     </row>
     <row r="12">
@@ -706,7 +1381,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4956</v>
+        <v>2.2666</v>
       </c>
     </row>
     <row r="13">
@@ -716,7 +1391,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3988</v>
+        <v>1.775</v>
       </c>
     </row>
     <row r="15">
@@ -779,6 +1454,34 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>Removal Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Metal Combinations Predicted</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Metals: Pb, Cd, Hg, As, Cr, Cu, Ni, Zn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Total Combinations: 96</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Note: Predicted removal/error capped at 0-99.0%</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3993,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -3389,13 +4092,13 @@
         <v>99.5</v>
       </c>
       <c r="J2" t="n">
-        <v>109.600985144183</v>
+        <v>99</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.10098514418303</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>10.10098514418303</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -3431,13 +4134,13 @@
         <v>54</v>
       </c>
       <c r="J3" t="n">
-        <v>58.1703158950359</v>
+        <v>58.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.170315895035898</v>
+        <v>-4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>4.170315895035898</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
@@ -3473,13 +4176,13 @@
         <v>83</v>
       </c>
       <c r="J4" t="n">
-        <v>82.42663035463241</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5733696453675918</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5733696453675918</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -3515,13 +4218,13 @@
         <v>95</v>
       </c>
       <c r="J5" t="n">
-        <v>95.36030911110913</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3603091111091317</v>
+        <v>-0.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3603091111091317</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -3557,13 +4260,13 @@
         <v>45</v>
       </c>
       <c r="J6" t="n">
-        <v>46.80486869660097</v>
+        <v>46.8</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.80486869660097</v>
+        <v>-1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.80486869660097</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -3599,13 +4302,13 @@
         <v>98</v>
       </c>
       <c r="J7" t="n">
-        <v>102.5071034598027</v>
+        <v>99</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.50710345980275</v>
+        <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>4.50710345980275</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3641,13 +4344,13 @@
         <v>80</v>
       </c>
       <c r="J8" t="n">
-        <v>78.19787633589289</v>
+        <v>78.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1.802123664107114</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.802123664107114</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -3683,13 +4386,13 @@
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>33.87118994012425</v>
+        <v>33.9</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.871189940124246</v>
+        <v>-3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>3.871189940124246</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -3698,6 +4401,5334 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Adsorbent</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>actual_removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>predicted_removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>error (%)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>absolute_error (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>79</v>
+      </c>
+      <c r="J4" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>120</v>
+      </c>
+      <c r="G5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" t="n">
+        <v>88</v>
+      </c>
+      <c r="J5" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" t="n">
+        <v>52</v>
+      </c>
+      <c r="J6" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="n">
+        <v>78</v>
+      </c>
+      <c r="J7" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>91</v>
+      </c>
+      <c r="J8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120</v>
+      </c>
+      <c r="G9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>96</v>
+      </c>
+      <c r="J9" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="n">
+        <v>61</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" t="n">
+        <v>97</v>
+      </c>
+      <c r="J12" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>120</v>
+      </c>
+      <c r="G13" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>99</v>
+      </c>
+      <c r="J13" t="n">
+        <v>99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" t="n">
+        <v>54</v>
+      </c>
+      <c r="J15" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" t="n">
+        <v>70</v>
+      </c>
+      <c r="J16" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="n">
+        <v>80</v>
+      </c>
+      <c r="J17" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>50</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45</v>
+      </c>
+      <c r="J18" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="n">
+        <v>69</v>
+      </c>
+      <c r="J19" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G20" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="n">
+        <v>83</v>
+      </c>
+      <c r="J20" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>120</v>
+      </c>
+      <c r="G21" t="n">
+        <v>200</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" t="n">
+        <v>90</v>
+      </c>
+      <c r="J21" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" t="n">
+        <v>55</v>
+      </c>
+      <c r="J22" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" t="n">
+        <v>80</v>
+      </c>
+      <c r="J23" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90</v>
+      </c>
+      <c r="G24" t="n">
+        <v>200</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" t="n">
+        <v>92</v>
+      </c>
+      <c r="J24" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>120</v>
+      </c>
+      <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" t="n">
+        <v>96</v>
+      </c>
+      <c r="J25" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" t="n">
+        <v>42</v>
+      </c>
+      <c r="J26" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" t="n">
+        <v>150</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="n">
+        <v>68</v>
+      </c>
+      <c r="J27" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90</v>
+      </c>
+      <c r="G28" t="n">
+        <v>200</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I28" t="n">
+        <v>83</v>
+      </c>
+      <c r="J28" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>120</v>
+      </c>
+      <c r="G29" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" t="n">
+        <v>50</v>
+      </c>
+      <c r="I29" t="n">
+        <v>91</v>
+      </c>
+      <c r="J29" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I30" t="n">
+        <v>60</v>
+      </c>
+      <c r="J30" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="n">
+        <v>150</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" t="n">
+        <v>85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>90</v>
+      </c>
+      <c r="G32" t="n">
+        <v>200</v>
+      </c>
+      <c r="H32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" t="n">
+        <v>95</v>
+      </c>
+      <c r="J32" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>120</v>
+      </c>
+      <c r="G33" t="n">
+        <v>200</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" t="n">
+        <v>98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>99</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" t="n">
+        <v>70</v>
+      </c>
+      <c r="J34" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>60</v>
+      </c>
+      <c r="G35" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" t="n">
+        <v>92</v>
+      </c>
+      <c r="J35" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>90</v>
+      </c>
+      <c r="G36" t="n">
+        <v>200</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" t="n">
+        <v>98</v>
+      </c>
+      <c r="J36" t="n">
+        <v>99</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>120</v>
+      </c>
+      <c r="G37" t="n">
+        <v>200</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>99</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Adsorbent</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>predicted_removal_percentage (%)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prediction_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>120</v>
+      </c>
+      <c r="G5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" t="n">
+        <v>99</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120</v>
+      </c>
+      <c r="G9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>120</v>
+      </c>
+      <c r="G13" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>50</v>
+      </c>
+      <c r="I18" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G20" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>120</v>
+      </c>
+      <c r="G21" t="n">
+        <v>200</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90</v>
+      </c>
+      <c r="G24" t="n">
+        <v>200</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>120</v>
+      </c>
+      <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" t="n">
+        <v>150</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90</v>
+      </c>
+      <c r="G28" t="n">
+        <v>200</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I28" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>120</v>
+      </c>
+      <c r="G29" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" t="n">
+        <v>50</v>
+      </c>
+      <c r="I29" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I30" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="n">
+        <v>150</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>90</v>
+      </c>
+      <c r="G32" t="n">
+        <v>200</v>
+      </c>
+      <c r="H32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>120</v>
+      </c>
+      <c r="G33" t="n">
+        <v>200</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>60</v>
+      </c>
+      <c r="G35" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>90</v>
+      </c>
+      <c r="G36" t="n">
+        <v>200</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>120</v>
+      </c>
+      <c r="G37" t="n">
+        <v>200</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>30</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" t="n">
+        <v>150</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>30</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>90</v>
+      </c>
+      <c r="G40" t="n">
+        <v>200</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50</v>
+      </c>
+      <c r="I40" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>120</v>
+      </c>
+      <c r="G41" t="n">
+        <v>200</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>30</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G43" t="n">
+        <v>150</v>
+      </c>
+      <c r="H43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I43" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>90</v>
+      </c>
+      <c r="G44" t="n">
+        <v>200</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>120</v>
+      </c>
+      <c r="G45" t="n">
+        <v>200</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>60</v>
+      </c>
+      <c r="G47" t="n">
+        <v>150</v>
+      </c>
+      <c r="H47" t="n">
+        <v>50</v>
+      </c>
+      <c r="I47" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>90</v>
+      </c>
+      <c r="G48" t="n">
+        <v>200</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50</v>
+      </c>
+      <c r="I48" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>120</v>
+      </c>
+      <c r="G49" t="n">
+        <v>200</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>25</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>30</v>
+      </c>
+      <c r="G50" t="n">
+        <v>100</v>
+      </c>
+      <c r="H50" t="n">
+        <v>50</v>
+      </c>
+      <c r="I50" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>25</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>60</v>
+      </c>
+      <c r="G51" t="n">
+        <v>150</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>30</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>90</v>
+      </c>
+      <c r="G52" t="n">
+        <v>200</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>35</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>120</v>
+      </c>
+      <c r="G53" t="n">
+        <v>200</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>25</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>30</v>
+      </c>
+      <c r="G54" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" t="n">
+        <v>150</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>30</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>90</v>
+      </c>
+      <c r="G56" t="n">
+        <v>200</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>120</v>
+      </c>
+      <c r="G57" t="n">
+        <v>200</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>30</v>
+      </c>
+      <c r="G58" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G59" t="n">
+        <v>150</v>
+      </c>
+      <c r="H59" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>90</v>
+      </c>
+      <c r="G60" t="n">
+        <v>200</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>120</v>
+      </c>
+      <c r="G61" t="n">
+        <v>200</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>30</v>
+      </c>
+      <c r="G62" t="n">
+        <v>100</v>
+      </c>
+      <c r="H62" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>60</v>
+      </c>
+      <c r="G63" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>30</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>90</v>
+      </c>
+      <c r="G64" t="n">
+        <v>200</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Biochar</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>35</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>120</v>
+      </c>
+      <c r="G65" t="n">
+        <v>200</v>
+      </c>
+      <c r="H65" t="n">
+        <v>50</v>
+      </c>
+      <c r="I65" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>25</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30</v>
+      </c>
+      <c r="G66" t="n">
+        <v>100</v>
+      </c>
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>60</v>
+      </c>
+      <c r="G67" t="n">
+        <v>150</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>30</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>90</v>
+      </c>
+      <c r="G68" t="n">
+        <v>200</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" t="n">
+        <v>99</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pb</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>35</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>200</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50</v>
+      </c>
+      <c r="I69" t="n">
+        <v>99</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>25</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>30</v>
+      </c>
+      <c r="G70" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50</v>
+      </c>
+      <c r="I70" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>60</v>
+      </c>
+      <c r="G71" t="n">
+        <v>150</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>90</v>
+      </c>
+      <c r="G72" t="n">
+        <v>200</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>35</v>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>120</v>
+      </c>
+      <c r="G73" t="n">
+        <v>200</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="n">
+        <v>99</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>30</v>
+      </c>
+      <c r="G74" t="n">
+        <v>100</v>
+      </c>
+      <c r="H74" t="n">
+        <v>50</v>
+      </c>
+      <c r="I74" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60</v>
+      </c>
+      <c r="G75" t="n">
+        <v>150</v>
+      </c>
+      <c r="H75" t="n">
+        <v>50</v>
+      </c>
+      <c r="I75" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>30</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="n">
+        <v>90</v>
+      </c>
+      <c r="G76" t="n">
+        <v>200</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>35</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>120</v>
+      </c>
+      <c r="G77" t="n">
+        <v>200</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" t="n">
+        <v>99</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>30</v>
+      </c>
+      <c r="G78" t="n">
+        <v>100</v>
+      </c>
+      <c r="H78" t="n">
+        <v>50</v>
+      </c>
+      <c r="I78" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>25</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>60</v>
+      </c>
+      <c r="G79" t="n">
+        <v>150</v>
+      </c>
+      <c r="H79" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>30</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>90</v>
+      </c>
+      <c r="G80" t="n">
+        <v>200</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>35</v>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>120</v>
+      </c>
+      <c r="G81" t="n">
+        <v>200</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" t="n">
+        <v>99</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D82" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>30</v>
+      </c>
+      <c r="G82" t="n">
+        <v>100</v>
+      </c>
+      <c r="H82" t="n">
+        <v>50</v>
+      </c>
+      <c r="I82" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>60</v>
+      </c>
+      <c r="G83" t="n">
+        <v>150</v>
+      </c>
+      <c r="H83" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>30</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>90</v>
+      </c>
+      <c r="G84" t="n">
+        <v>200</v>
+      </c>
+      <c r="H84" t="n">
+        <v>50</v>
+      </c>
+      <c r="I84" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>120</v>
+      </c>
+      <c r="G85" t="n">
+        <v>200</v>
+      </c>
+      <c r="H85" t="n">
+        <v>50</v>
+      </c>
+      <c r="I85" t="n">
+        <v>99</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>25</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>30</v>
+      </c>
+      <c r="G86" t="n">
+        <v>100</v>
+      </c>
+      <c r="H86" t="n">
+        <v>50</v>
+      </c>
+      <c r="I86" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>25</v>
+      </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" t="n">
+        <v>60</v>
+      </c>
+      <c r="G87" t="n">
+        <v>150</v>
+      </c>
+      <c r="H87" t="n">
+        <v>50</v>
+      </c>
+      <c r="I87" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>30</v>
+      </c>
+      <c r="E88" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" t="n">
+        <v>90</v>
+      </c>
+      <c r="G88" t="n">
+        <v>200</v>
+      </c>
+      <c r="H88" t="n">
+        <v>50</v>
+      </c>
+      <c r="I88" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>35</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="n">
+        <v>120</v>
+      </c>
+      <c r="G89" t="n">
+        <v>200</v>
+      </c>
+      <c r="H89" t="n">
+        <v>50</v>
+      </c>
+      <c r="I89" t="n">
+        <v>99</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>25</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>30</v>
+      </c>
+      <c r="G90" t="n">
+        <v>100</v>
+      </c>
+      <c r="H90" t="n">
+        <v>50</v>
+      </c>
+      <c r="I90" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>25</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>60</v>
+      </c>
+      <c r="G91" t="n">
+        <v>150</v>
+      </c>
+      <c r="H91" t="n">
+        <v>50</v>
+      </c>
+      <c r="I91" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>30</v>
+      </c>
+      <c r="E92" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" t="n">
+        <v>90</v>
+      </c>
+      <c r="G92" t="n">
+        <v>200</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50</v>
+      </c>
+      <c r="I92" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>35</v>
+      </c>
+      <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>120</v>
+      </c>
+      <c r="G93" t="n">
+        <v>200</v>
+      </c>
+      <c r="H93" t="n">
+        <v>50</v>
+      </c>
+      <c r="I93" t="n">
+        <v>99</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D94" t="n">
+        <v>25</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>30</v>
+      </c>
+      <c r="G94" t="n">
+        <v>100</v>
+      </c>
+      <c r="H94" t="n">
+        <v>50</v>
+      </c>
+      <c r="I94" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>25</v>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>60</v>
+      </c>
+      <c r="G95" t="n">
+        <v>150</v>
+      </c>
+      <c r="H95" t="n">
+        <v>50</v>
+      </c>
+      <c r="I95" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>30</v>
+      </c>
+      <c r="E96" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>90</v>
+      </c>
+      <c r="G96" t="n">
+        <v>200</v>
+      </c>
+      <c r="H96" t="n">
+        <v>50</v>
+      </c>
+      <c r="I96" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>35</v>
+      </c>
+      <c r="E97" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" t="n">
+        <v>120</v>
+      </c>
+      <c r="G97" t="n">
+        <v>200</v>
+      </c>
+      <c r="H97" t="n">
+        <v>50</v>
+      </c>
+      <c r="I97" t="n">
+        <v>99</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Synthetic (All Metal Combinations)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3735,10 +9766,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9824822628630567</v>
+        <v>0.9877616136121325</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9673641167306626</v>
+        <v>0.9917040401173243</v>
       </c>
     </row>
     <row r="3">
@@ -3748,10 +9779,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.134551537479444</v>
+        <v>3.587142857142855</v>
       </c>
       <c r="C3" t="n">
-        <v>20.21066310197032</v>
+        <v>5.137499999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3761,10 +9792,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.265954884255078</v>
+        <v>1.893975410912944</v>
       </c>
       <c r="C4" t="n">
-        <v>4.495627108865938</v>
+        <v>2.266605391328627</v>
       </c>
     </row>
     <row r="5">
@@ -3774,10 +9805,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.867653730387352</v>
+        <v>1.564285714285715</v>
       </c>
       <c r="C5" t="n">
-        <v>3.398783194541341</v>
+        <v>1.774999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +9816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3975,677 +10006,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dosage (g/L)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Temp (°C)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Time (min)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>C0 (mg/L)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ce (mg/L)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>removal_percentage (%)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qe (mg/g)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36</v>
-      </c>
-      <c r="I2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J2" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C3" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" t="n">
-        <v>11.75694444444444</v>
-      </c>
-      <c r="I3" t="n">
-        <v>76.48611111111111</v>
-      </c>
-      <c r="J3" t="n">
-        <v>35.07061111111111</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.5669467095138409</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.20458932936041</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.242118006816238</v>
-      </c>
-      <c r="E4" t="n">
-        <v>34.01680257083045</v>
-      </c>
-      <c r="F4" t="n">
-        <v>42.04589329360411</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9.740102322561517</v>
-      </c>
-      <c r="I4" t="n">
-        <v>19.48020464512303</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12.42200022144531</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="C6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>24.84375</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>75</v>
-      </c>
-      <c r="F7" t="n">
-        <v>175</v>
-      </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31.5835</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="C8" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>200</v>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="I8" t="n">
-        <v>92</v>
-      </c>
-      <c r="J8" t="n">
-        <v>42.125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>120</v>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H9" t="n">
-        <v>35</v>
-      </c>
-      <c r="I9" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dosage (g/L)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Temp (°C)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Time (min)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>C0 (mg/L)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ce (mg/L)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>removal_percentage (%)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qe (mg/g)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dosage (g/L)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9438798074485388</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9128709291752771</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9438798074485392</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.8191084467312126</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8191084467312126</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.817176499196376</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9438798074485388</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.7385489458759963</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9438798074485387</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.8181818181818181</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.6939553253752606</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.6939553253752606</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.7261631278865359</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9128709291752771</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7385489458759963</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9128709291752768</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9847319278346622</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.8495841102831636</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8495841102831634</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.8035728671246343</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Time (min)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9438798074485387</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9128709291752768</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9438798074485392</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.8191084467312125</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8191084467312125</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.8171764991963759</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9438798074485392</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8181818181818181</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9847319278346622</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9438798074485392</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.8443886192831871</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8443886192831872</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.8112383490526567</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C0 (mg/L)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ce (mg/L)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.8191084467312126</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.6939553253752606</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.8495841102831636</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.8191084467312125</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.8443886192831871</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.4445206645340559</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>removal_percentage (%)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8191084467312126</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6939553253752606</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8495841102831634</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8191084467312125</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8443886192831872</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.444520664534056</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>qe (mg/g)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.817176499196376</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.7261631278865359</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.8035728671246343</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.8171764991963759</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.8112383490526567</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4445206645340559</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.444520664534056</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/chemical_adsorbent_report.xlsx
+++ b/chemical_adsorbent_report.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Visualizations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dataset" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Training Data" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Testing &amp; Predictions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="All Predictions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Metal Combinations" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Model Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Coefficients" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Statistical Summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Correlation Matrix" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Graph Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="All Predictions Graphs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dataset" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Training Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Testing &amp; Predictions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="All Predictions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Metal Combinations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Model Metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Coefficients" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Statistical Summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Correlation Matrix" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Graph Analysis" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -191,6 +192,89 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="15240000" cy="10668000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="7620000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12192000" cy="6096000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -507,6 +591,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Abs_Coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metal_Mn</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-10.98707973244456</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10.98707973244456</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metal_Pb</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9.040480708412423</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9.040480708412423</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adsorbent_Biochar</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-6.105736842622738</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.105736842622738</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adsorbent_Chitosan composite</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.881827924216666</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.881827924216666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Temp (°C)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-2.309184105167655</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.309184105167655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Metal_Cu</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.946599024032162</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.946599024032162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Time (min)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6229174631890663</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6229174631890663</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4844557363162729</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4844557363162729</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Adsorbent_Activated Carbon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2239089184060762</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2239089184060762</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.09274999215494417</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.09274999215494417</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dosage (g/L)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01038195771982011</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01038195771982011</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C0 (mg/L)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -846,7 +1122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1174,7 +1450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1491,6 +1767,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2978,7 +3268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3974,7 +4264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4400,7 +4690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6002,7 +6292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9728,7 +10018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9814,196 +10104,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Coefficient</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Abs_Coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Metal_Mn</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>-10.98707973244456</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10.98707973244456</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Metal_Pb</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>9.040480708412423</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9.040480708412423</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Adsorbent_Biochar</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-6.105736842622738</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6.105736842622738</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Adsorbent_Chitosan composite</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5.881827924216666</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5.881827924216666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-2.309184105167655</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.309184105167655</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Metal_Cu</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.946599024032162</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.946599024032162</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Time (min)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6229174631890663</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6229174631890663</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.4844557363162729</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.4844557363162729</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Adsorbent_Activated Carbon</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.2239089184060762</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2239089184060762</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.09274999215494417</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.09274999215494417</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dosage (g/L)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.01038195771982011</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.01038195771982011</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C0 (mg/L)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>